--- a/data/trans_dic/P32E$bar_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32E$bar_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>62,63; 89,95</t>
+          <t>62,9; 90,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,21; 88,29</t>
+          <t>31,21; 86,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,53; 87,29</t>
+          <t>60,41; 86,09</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,18; 77,05</t>
+          <t>36,31; 76,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74,56; 96,23</t>
+          <t>74,02; 95,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,42; 82,72</t>
+          <t>55,77; 81,42</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,08; 63,13</t>
+          <t>21,64; 65,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,86; 100,0</t>
+          <t>61,88; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,65; 69,62</t>
+          <t>30,07; 71,28</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60,74; 84,76</t>
+          <t>60,54; 85,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,87; 79,78</t>
+          <t>26,97; 79,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57,07; 79,82</t>
+          <t>58,42; 79,81</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,44; 74,16</t>
+          <t>58,04; 75,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,81; 83,98</t>
+          <t>59,73; 84,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61,77; 74,96</t>
+          <t>61,79; 75,46</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21389; 30715</t>
+          <t>21480; 30807</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3699; 9545</t>
+          <t>3374; 9308</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28112; 39247</t>
+          <t>27159; 38705</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11574; 24651</t>
+          <t>11618; 24634</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16102; 20782</t>
+          <t>15985; 20707</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30235; 44331</t>
+          <t>29887; 43634</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5529; 15119</t>
+          <t>5183; 15701</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2941; 4755</t>
+          <t>2943; 4755</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8223; 19984</t>
+          <t>8632; 20461</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32811; 45785</t>
+          <t>32701; 46049</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4892; 14003</t>
+          <t>4735; 13908</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40843; 57129</t>
+          <t>41813; 57125</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>82776; 106876</t>
+          <t>83638; 108288</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32177; 45948</t>
+          <t>32683; 46372</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>122822; 149033</t>
+          <t>122849; 150025</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$bar_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32E$bar_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>62,9; 90,22</t>
+          <t>62,08; 90,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,21; 86,09</t>
+          <t>34,58; 87,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,41; 86,09</t>
+          <t>63,22; 87,22</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,31; 76,99</t>
+          <t>39,23; 75,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74,02; 95,89</t>
+          <t>73,97; 95,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,77; 81,42</t>
+          <t>55,63; 81,23</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>49,8%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,64; 65,56</t>
+          <t>25,65; 66,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,88; 100,0</t>
+          <t>24,57; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,07; 71,28</t>
+          <t>31,77; 67,73</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>68,43%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60,54; 85,25</t>
+          <t>59,15; 83,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,97; 79,23</t>
+          <t>31,36; 78,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,42; 79,81</t>
+          <t>56,06; 78,28</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>67,53%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>58,04; 75,14</t>
+          <t>56,91; 72,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>59,73; 84,75</t>
+          <t>58,67; 81,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61,79; 75,46</t>
+          <t>60,83; 73,8</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27182</t>
+          <t>27859</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34199</t>
+          <t>34999</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21480; 30807</t>
+          <t>21715; 31799</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3374; 9308</t>
+          <t>3837; 9721</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27159; 38705</t>
+          <t>29129; 40187</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>18750</t>
+          <t>22873</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19136</t>
+          <t>22234</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37886</t>
+          <t>45106</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11618; 24634</t>
+          <t>15242; 29185</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15985; 20707</t>
+          <t>18635; 24129</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29887; 43634</t>
+          <t>35626; 52023</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10061</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14494</t>
+          <t>18118</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5183; 15701</t>
+          <t>7729; 20039</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2943; 4755</t>
+          <t>1535; 6248</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8632; 20461</t>
+          <t>11558; 24642</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>39960</t>
+          <t>41857</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50071</t>
+          <t>54175</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32701; 46049</t>
+          <t>34022; 48292</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4735; 13908</t>
+          <t>6789; 17024</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41813; 57125</t>
+          <t>44384; 61975</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>95952</t>
+          <t>106085</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40698</t>
+          <t>46314</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>136649</t>
+          <t>152399</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>83638; 108288</t>
+          <t>91893; 117638</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32683; 46372</t>
+          <t>37657; 52305</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>122849; 150025</t>
+          <t>137276; 166546</t>
         </is>
       </c>
     </row>
